--- a/public/exports-from-60-with-coowners/58271713.xlsx
+++ b/public/exports-from-60-with-coowners/58271713.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027402</t>
+          <t xml:space="preserve">200027403</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">310007201</t>
+          <t xml:space="preserve">310007202</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311662005</t>
+          <t xml:space="preserve">311662099</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">

--- a/public/exports-from-60-with-coowners/58271713.xlsx
+++ b/public/exports-from-60-with-coowners/58271713.xlsx
@@ -3289,7 +3289,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027403</t>
+          <t xml:space="preserve">200027402</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">310007202</t>
+          <t xml:space="preserve">310007201</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311662099</t>
+          <t xml:space="preserve">311662005</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
